--- a/期刊实地位置.xlsx
+++ b/期刊实地位置.xlsx
@@ -29,7 +29,22 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="122">
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>A3</t>
+  </si>
+  <si>
+    <t>A4</t>
+  </si>
+  <si>
+    <t>A5</t>
+  </si>
   <si>
     <t>C 环球人物</t>
   </si>
@@ -85,6 +100,21 @@
     <t>F 商业周刊</t>
   </si>
   <si>
+    <t>B1</t>
+  </si>
+  <si>
+    <t>B2</t>
+  </si>
+  <si>
+    <t>B3</t>
+  </si>
+  <si>
+    <t>B4</t>
+  </si>
+  <si>
+    <t>B5</t>
+  </si>
+  <si>
     <t>F 证券市场周刊</t>
   </si>
   <si>
@@ -163,6 +193,21 @@
     <t>I 读书</t>
   </si>
   <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>C4</t>
+  </si>
+  <si>
+    <t>C5</t>
+  </si>
+  <si>
     <t>I 世界文学</t>
   </si>
   <si>
@@ -251,6 +296,21 @@
   </si>
   <si>
     <t>K 华夏地理</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>D2</t>
+  </si>
+  <si>
+    <t>D3</t>
+  </si>
+  <si>
+    <t>D4</t>
+  </si>
+  <si>
+    <t>D5</t>
   </si>
   <si>
     <t>K 纵横</t>
@@ -712,7 +772,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -724,6 +784,32 @@
       <left style="thin">
         <color rgb="FFD9D9D9"/>
       </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FFD9D9D9"/>
       </right>
@@ -859,7 +945,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
@@ -871,34 +957,34 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
@@ -983,7 +1069,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -996,8 +1082,20 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1310,427 +1408,621 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:10">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:14">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="J1" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="K1" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="M1" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="N1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="16.5" spans="1:10">
-      <c r="A2" s="3" t="s">
+    <row r="2" ht="16.5" spans="1:14">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2"/>
+      <c r="D2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="2"/>
+      <c r="G2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="H2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="K2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="N2" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" ht="16.5" spans="1:14">
+      <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="B3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="3" ht="16.5" spans="1:10">
-      <c r="A3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="2" t="s">
+    <row r="4" ht="16.5" spans="1:14">
+      <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="4" ht="16.5" spans="1:10">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
+    <row r="5" ht="16.5" spans="1:14">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
     </row>
-    <row r="5" ht="16.5" spans="1:10">
-      <c r="A5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" s="3" t="s">
+    <row r="6" ht="16.5" spans="1:14">
+      <c r="A6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="C6" s="2"/>
+      <c r="D6" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="E6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="2"/>
+      <c r="G6" s="4" t="s">
         <v>25</v>
       </c>
+      <c r="H6" s="5"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L6" s="2"/>
+      <c r="M6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="6" ht="16.5" spans="1:10">
-      <c r="A6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="2" t="s">
+    <row r="7" ht="16.5" spans="1:14">
+      <c r="A7" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="B7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="E7" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="F7" s="3"/>
+      <c r="G7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="2" t="s">
+      <c r="H7" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="I7" s="3"/>
+      <c r="J7" s="3" t="s">
         <v>33</v>
       </c>
+      <c r="K7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="7" ht="16.5" spans="1:10">
-      <c r="A7" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" s="3" t="s">
+    <row r="8" ht="16.5" spans="1:14">
+      <c r="A8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="B8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E8" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F8" s="2"/>
+      <c r="G8" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="H8" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="I8" s="2"/>
+      <c r="J8" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="K8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="N8" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
+    <row r="9" ht="16.5" spans="1:14">
+      <c r="A9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>53</v>
+      </c>
     </row>
-    <row r="9" ht="16.5" spans="1:10">
-      <c r="A9" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>53</v>
-      </c>
+    <row r="10" s="1" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
     </row>
-    <row r="10" ht="16.5" spans="1:10">
-      <c r="A10" s="3" t="s">
+    <row r="11" s="1" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A11" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B11" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="6"/>
+      <c r="D11" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="E11" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F11" s="6"/>
+      <c r="G11" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="H11" s="8"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="K11" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="L11" s="6"/>
+      <c r="M11" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="N11" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" ht="16.5" spans="1:14">
+      <c r="A12" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="C12" s="2"/>
+      <c r="D12" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="E12" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="F12" s="2"/>
+      <c r="G12" s="2" t="s">
         <v>63</v>
       </c>
+      <c r="H12" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>68</v>
+      </c>
     </row>
-    <row r="11" ht="16.5" spans="1:10">
-      <c r="A11" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F11" s="2" t="s">
+    <row r="13" ht="16.5" spans="1:14">
+      <c r="A13" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="C13" s="3"/>
+      <c r="D13" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="E13" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="F13" s="3"/>
+      <c r="G13" s="3" t="s">
         <v>73</v>
       </c>
+      <c r="H13" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>78</v>
+      </c>
     </row>
-    <row r="12" ht="16.5" spans="1:10">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
+    <row r="14" ht="16.5" spans="1:14">
+      <c r="A14" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>88</v>
+      </c>
     </row>
-    <row r="13" ht="16.5" spans="1:10">
-      <c r="A13" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>83</v>
-      </c>
+    <row r="15" ht="16.5" spans="1:14">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
     </row>
-    <row r="14" ht="16.5" spans="1:10">
-      <c r="A14" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F14" s="2" t="s">
+    <row r="16" ht="16.5" spans="1:14">
+      <c r="A16" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="B16" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="E16" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F16" s="2"/>
+      <c r="G16" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="I14" s="2" t="s">
+      <c r="H16" s="5"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="J14" s="2" t="s">
+      <c r="K16" s="4" t="s">
         <v>92</v>
       </c>
+      <c r="L16" s="2"/>
+      <c r="M16" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="N16" s="4" t="s">
+        <v>93</v>
+      </c>
     </row>
-    <row r="15" ht="16.5" spans="1:10">
-      <c r="A15" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="B15" s="3" t="s">
+    <row r="17" ht="16.5" spans="1:14">
+      <c r="A17" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="B17" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="C17" s="3"/>
+      <c r="D17" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E17" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F17" s="3"/>
+      <c r="G17" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="H17" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="H15" s="3" t="s">
+      <c r="I17" s="3"/>
+      <c r="J17" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="K17" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>101</v>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="18" ht="16.5" spans="1:14">
+      <c r="A18" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="19" ht="16.5" spans="1:14">
+      <c r="A19" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>
